--- a/quote_forms/031_hire_inquiry_form--quote_forms.xlsx
+++ b/quote_forms/031_hire_inquiry_form--quote_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -754,8 +754,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -783,12 +783,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'food',_'value':_'food'}</t>
+          <t>food</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'Food', 'value': 'food'}</t>
+          <t>Food</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'package',_'value':_'package'}</t>
+          <t>package</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'Package', 'value': 'package'}</t>
+          <t>Package</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'both',_'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 'Both', 'value': 'both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_13,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 13, 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_14,_'label':_'less_than_1_hour',_'value':_'less_than_1_hour'}</t>
+          <t>less_than_1_hour</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 14, 'label': 'Less than 1 hour', 'value': 'less_than_1_hour'}</t>
+          <t>Less than 1 hour</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_15,_'label':_'1-2_hours',_'value':_'one_to_two_hours'}</t>
+          <t>1-2_hours</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 15, 'label': '1-2 hours', 'value': 'one_to_two_hours'}</t>
+          <t>1-2 hours</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_16,_'label':_'2-4_hours',_'value':_'two_to_four_hours'}</t>
+          <t>2-4_hours</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 16, 'label': '2-4 hours', 'value': 'two_to_four_hours'}</t>
+          <t>2-4 hours</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_17,_'label':_'more_than_4_hours',_'value':_'more_than_4_hours'}</t>
+          <t>more_than_4_hours</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 17, 'label': 'More than 4 hours', 'value': 'more_than_4_hours'}</t>
+          <t>More than 4 hours</t>
         </is>
       </c>
     </row>
